--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104758_W34.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104758_W34.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>P. ORIOLA</t>
+          <t>A. UBAL</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.2531</v>
+        <v>5.9162</v>
       </c>
       <c r="E2" t="n">
-        <v>5.1143</v>
+        <v>4.3101</v>
       </c>
       <c r="F2" t="n">
-        <v>2.1388</v>
+        <v>1.6062</v>
       </c>
       <c r="G2" t="n">
-        <v>1.2034</v>
+        <v>3.2996</v>
       </c>
       <c r="H2" t="n">
-        <v>1.2522</v>
+        <v>2.5562</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.0488</v>
+        <v>0.7433999999999999</v>
       </c>
       <c r="J2" t="n">
-        <v>1.717</v>
+        <v>3.4556</v>
       </c>
       <c r="K2" t="n">
-        <v>1.7991</v>
+        <v>3.0164</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.08210000000000001</v>
+        <v>0.4392</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.5135999999999999</v>
+        <v>-0.156</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.5469000000000001</v>
+        <v>-0.4603</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0333</v>
+        <v>0.3043</v>
       </c>
       <c r="P2" t="n">
+        <v>0.6829</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>-1.1382</v>
+      </c>
+      <c r="R2" t="n">
         <v>1.8211</v>
       </c>
-      <c r="Q2" t="n">
-        <v>-0.2276</v>
-      </c>
-      <c r="R2" t="n">
-        <v>2.0487</v>
-      </c>
       <c r="S2" t="n">
-        <v>3.6839</v>
+        <v>-0.403</v>
       </c>
       <c r="T2" t="n">
-        <v>2.3777</v>
+        <v>-0.3441</v>
       </c>
       <c r="U2" t="n">
-        <v>1.3062</v>
+        <v>-0.0589</v>
       </c>
       <c r="V2" t="n">
-        <v>0.5447</v>
+        <v>2.3367</v>
       </c>
       <c r="W2" t="n">
-        <v>1.2472</v>
+        <v>2.3367</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.7025</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. UBAL</t>
+          <t>P. ORIOLA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.5366</v>
+        <v>5.1487</v>
       </c>
       <c r="E3" t="n">
-        <v>3.8363</v>
+        <v>3.5745</v>
       </c>
       <c r="F3" t="n">
-        <v>1.7003</v>
+        <v>1.5742</v>
       </c>
       <c r="G3" t="n">
-        <v>3.2996</v>
+        <v>1.2034</v>
       </c>
       <c r="H3" t="n">
-        <v>2.5562</v>
+        <v>1.2522</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7433999999999999</v>
+        <v>-0.0488</v>
       </c>
       <c r="J3" t="n">
-        <v>3.4556</v>
+        <v>1.717</v>
       </c>
       <c r="K3" t="n">
-        <v>3.0164</v>
+        <v>1.7991</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4392</v>
+        <v>-0.08210000000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.156</v>
+        <v>-0.5135999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.4603</v>
+        <v>-0.5469000000000001</v>
       </c>
       <c r="O3" t="n">
-        <v>0.3043</v>
+        <v>0.0333</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6829</v>
+        <v>1.8211</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1382</v>
+        <v>-0.2276</v>
       </c>
       <c r="R3" t="n">
-        <v>1.8211</v>
+        <v>2.0487</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.7827</v>
+        <v>1.5795</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8179</v>
+        <v>0.8379</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0352</v>
+        <v>0.7416</v>
       </c>
       <c r="V3" t="n">
-        <v>2.3367</v>
+        <v>0.5447</v>
       </c>
       <c r="W3" t="n">
-        <v>2.3367</v>
+        <v>1.2472</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.4174</v>
+        <v>4.6229</v>
       </c>
       <c r="E4" t="n">
-        <v>0.449</v>
+        <v>1.2781</v>
       </c>
       <c r="F4" t="n">
-        <v>2.9684</v>
+        <v>3.3448</v>
       </c>
       <c r="G4" t="n">
         <v>-0.0456</v>
@@ -766,13 +766,13 @@
         <v>3.1868</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.7433999999999999</v>
+        <v>0.4621</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1492</v>
+        <v>0.68</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.5943000000000001</v>
+        <v>-0.2179</v>
       </c>
       <c r="V4" t="n">
         <v>1.2472</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.174</v>
+        <v>2.6234</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.1099</v>
+        <v>-0.7544999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>3.2838</v>
+        <v>3.3779</v>
       </c>
       <c r="G5" t="n">
         <v>-0.3426</v>
@@ -844,13 +844,13 @@
         <v>2.2763</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9036</v>
+        <v>1.353</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3573</v>
+        <v>0.7126</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5463</v>
+        <v>0.6404</v>
       </c>
       <c r="V5" t="n">
         <v>0.7025</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>G. KNUDSEN</t>
+          <t>K. AKOBUNDU</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.6287</v>
+        <v>1.3631</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.4653</v>
+        <v>0.8325</v>
       </c>
       <c r="F6" t="n">
-        <v>3.0939</v>
+        <v>0.5305</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.9362</v>
+        <v>2.2288</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.3969</v>
+        <v>1.1977</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5393</v>
+        <v>1.031</v>
       </c>
       <c r="J6" t="n">
-        <v>-2.0131</v>
+        <v>2.6008</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2068</v>
+        <v>1.9305</v>
       </c>
       <c r="L6" t="n">
-        <v>-2.22</v>
+        <v>0.6703</v>
       </c>
       <c r="M6" t="n">
-        <v>1.077</v>
+        <v>-0.372</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.6037</v>
+        <v>-0.7328</v>
       </c>
       <c r="O6" t="n">
-        <v>1.6807</v>
+        <v>0.3608</v>
       </c>
       <c r="P6" t="n">
-        <v>1.1382</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-2.2763</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1382</v>
+        <v>1.8211</v>
       </c>
       <c r="S6" t="n">
-        <v>1.5845</v>
+        <v>0.3635</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5479000000000001</v>
+        <v>0.1925</v>
       </c>
       <c r="U6" t="n">
-        <v>1.0366</v>
+        <v>0.171</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.1578</v>
+        <v>-0.7739</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.3155</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1578</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>K. AKOBUNDU</t>
+          <t>G. KNUDSEN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0531</v>
+        <v>1.1268</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2403</v>
+        <v>-1.4653</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8128</v>
+        <v>2.5921</v>
       </c>
       <c r="G7" t="n">
-        <v>2.2288</v>
+        <v>-0.9362</v>
       </c>
       <c r="H7" t="n">
-        <v>1.1977</v>
+        <v>-0.3969</v>
       </c>
       <c r="I7" t="n">
-        <v>1.031</v>
+        <v>-0.5393</v>
       </c>
       <c r="J7" t="n">
-        <v>2.6008</v>
+        <v>-2.0131</v>
       </c>
       <c r="K7" t="n">
-        <v>1.9305</v>
+        <v>0.2068</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6703</v>
+        <v>-2.22</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.372</v>
+        <v>1.077</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.7328</v>
+        <v>-0.6037</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3608</v>
+        <v>1.6807</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.4553</v>
+        <v>1.1382</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.2763</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.8211</v>
+        <v>1.1382</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0536</v>
+        <v>1.0826</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3997</v>
+        <v>0.5479000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4533</v>
+        <v>0.5347</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.7739</v>
+        <v>-0.1578</v>
       </c>
       <c r="W7" t="n">
-        <v>0.3155</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.0895</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6817</v>
+        <v>0.5876</v>
       </c>
       <c r="E8" t="n">
         <v>0.0392</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6425</v>
+        <v>0.5484</v>
       </c>
       <c r="G8" t="n">
         <v>0.3959</v>
@@ -1078,13 +1078,13 @@
         <v>0.2276</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0582</v>
+        <v>-0.0359</v>
       </c>
       <c r="T8" t="n">
         <v>-0.0697</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1279</v>
+        <v>0.0338</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.1477</v>
+        <v>-0.9735</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.007</v>
+        <v>-2.7701</v>
       </c>
       <c r="F9" t="n">
-        <v>1.8594</v>
+        <v>1.7966</v>
       </c>
       <c r="G9" t="n">
         <v>-0.646</v>
@@ -1156,13 +1156,13 @@
         <v>1.1382</v>
       </c>
       <c r="S9" t="n">
-        <v>0.7064</v>
+        <v>0.8804999999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0838</v>
+        <v>0.1531</v>
       </c>
       <c r="U9" t="n">
-        <v>0.7902</v>
+        <v>0.7275</v>
       </c>
       <c r="V9" t="n">
         <v>0.1578</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. DUKE JR</t>
+          <t>D. PEREZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.7663</v>
+        <v>-2.4552</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.9316</v>
+        <v>0.2822</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.8348</v>
+        <v>-2.7375</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.8413</v>
+        <v>1.7375</v>
       </c>
       <c r="H10" t="n">
-        <v>-3.5434</v>
+        <v>1.6142</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2979</v>
+        <v>0.1233</v>
       </c>
       <c r="J10" t="n">
-        <v>-3.0086</v>
+        <v>3.0279</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.2935</v>
+        <v>3.0509</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.7151999999999999</v>
+        <v>-0.023</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.8326</v>
+        <v>-1.2904</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.2499</v>
+        <v>-1.4367</v>
       </c>
       <c r="O10" t="n">
-        <v>0.4173</v>
+        <v>0.1463</v>
       </c>
       <c r="P10" t="n">
-        <v>0.4553</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1382</v>
+        <v>-2.2763</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5934</v>
+        <v>0.6829</v>
       </c>
       <c r="S10" t="n">
-        <v>1.7091</v>
+        <v>-0.4204</v>
       </c>
       <c r="T10" t="n">
-        <v>2.0575</v>
+        <v>-0.4694</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3483</v>
+        <v>0.049</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.0895</v>
+        <v>-2.1789</v>
       </c>
       <c r="W10" t="n">
-        <v>0.1578</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.2472</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D. PEREZ</t>
+          <t>E. BROOKS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,58 +1267,58 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.7689</v>
+        <v>-2.6813</v>
       </c>
       <c r="E11" t="n">
-        <v>0.2822</v>
+        <v>-1.8502</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.0511</v>
+        <v>-0.8312</v>
       </c>
       <c r="G11" t="n">
-        <v>1.7375</v>
+        <v>-0.8937</v>
       </c>
       <c r="H11" t="n">
-        <v>1.6142</v>
+        <v>-0.764</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1233</v>
+        <v>-0.1297</v>
       </c>
       <c r="J11" t="n">
-        <v>3.0279</v>
+        <v>-0.4074</v>
       </c>
       <c r="K11" t="n">
-        <v>3.0509</v>
+        <v>-0.1314</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.023</v>
+        <v>-0.276</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.2904</v>
+        <v>-0.4863</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.4367</v>
+        <v>-0.6326000000000001</v>
       </c>
       <c r="O11" t="n">
         <v>0.1463</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.5934</v>
+        <v>0.9105</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.2763</v>
+        <v>-1.1382</v>
       </c>
       <c r="R11" t="n">
-        <v>0.6829</v>
+        <v>2.0487</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7341</v>
+        <v>-0.5192</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4694</v>
+        <v>-0.3046</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2647</v>
+        <v>-0.2146</v>
       </c>
       <c r="V11" t="n">
         <v>-2.1789</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>E. BROOKS</t>
+          <t>D. DUKE JR</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.9079</v>
+        <v>-3.5257</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.7317</v>
+        <v>-2.8791</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.1762</v>
+        <v>-0.6466</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.8937</v>
+        <v>-3.8413</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.764</v>
+        <v>-3.5434</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1297</v>
+        <v>-0.2979</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.4074</v>
+        <v>-3.0086</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.1314</v>
+        <v>-2.2935</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.276</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.4863</v>
+        <v>-0.8326</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.6326000000000001</v>
+        <v>-1.2499</v>
       </c>
       <c r="O12" t="n">
-        <v>0.1463</v>
+        <v>0.4173</v>
       </c>
       <c r="P12" t="n">
-        <v>0.9105</v>
+        <v>0.4553</v>
       </c>
       <c r="Q12" t="n">
         <v>-1.1382</v>
       </c>
       <c r="R12" t="n">
-        <v>2.0487</v>
+        <v>1.5934</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7458</v>
+        <v>0.9498</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1862</v>
+        <v>1.1099</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5596</v>
+        <v>-0.1601</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.1789</v>
+        <v>-1.0895</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.1789</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.9276</v>
+        <v>-3.5268</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.9333</v>
+        <v>-4.8148</v>
       </c>
       <c r="F13" t="n">
-        <v>1.0057</v>
+        <v>1.288</v>
       </c>
       <c r="G13" t="n">
         <v>-3.9637</v>
@@ -1468,13 +1468,13 @@
         <v>2.5039</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.3509</v>
+        <v>0.0498</v>
       </c>
       <c r="T13" t="n">
-        <v>0.06</v>
+        <v>0.1784</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.4109</v>
+        <v>-0.1286</v>
       </c>
       <c r="V13" t="n">
         <v>0.387</v>
@@ -1504,16 +1504,16 @@
         <v>8.226199999999997</v>
       </c>
       <c r="E14" t="n">
-        <v>-4.2175</v>
+        <v>-4.2174</v>
       </c>
       <c r="F14" t="n">
-        <v>12.4435</v>
+        <v>12.4434</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.803899999999999</v>
+        <v>-1.8039</v>
       </c>
       <c r="H14" t="n">
-        <v>0.7894999999999996</v>
+        <v>0.7894999999999992</v>
       </c>
       <c r="I14" t="n">
         <v>-2.5935</v>
@@ -1525,13 +1525,13 @@
         <v>8.122000000000002</v>
       </c>
       <c r="L14" t="n">
-        <v>-6.9326</v>
+        <v>-6.932600000000001</v>
       </c>
       <c r="M14" t="n">
         <v>-2.9931</v>
       </c>
       <c r="N14" t="n">
-        <v>-7.3325</v>
+        <v>-7.332500000000001</v>
       </c>
       <c r="O14" t="n">
         <v>4.339300000000001</v>
@@ -1546,10 +1546,10 @@
         <v>20.4869</v>
       </c>
       <c r="S14" t="n">
-        <v>5.3424</v>
+        <v>5.3423</v>
       </c>
       <c r="T14" t="n">
-        <v>3.2245</v>
+        <v>3.224500000000001</v>
       </c>
       <c r="U14" t="n">
         <v>2.1179</v>
@@ -1561,13 +1561,13 @@
         <v>6.1647</v>
       </c>
       <c r="X14" t="n">
-        <v>-7.1678</v>
+        <v>-7.167800000000002</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>I. ALMANSA</t>
+          <t>A. ABALDE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.0463</v>
+        <v>2.6116</v>
       </c>
       <c r="E15" t="n">
-        <v>5.6164</v>
+        <v>0.3495</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.5702</v>
+        <v>2.2621</v>
       </c>
       <c r="G15" t="n">
-        <v>3.1452</v>
+        <v>3.5275</v>
       </c>
       <c r="H15" t="n">
-        <v>2.5534</v>
+        <v>0.1263</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5919</v>
+        <v>3.4013</v>
       </c>
       <c r="J15" t="n">
-        <v>3.1854</v>
+        <v>2.1027</v>
       </c>
       <c r="K15" t="n">
-        <v>2.9992</v>
+        <v>0.4719</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1862</v>
+        <v>1.6308</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.0402</v>
+        <v>1.4249</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.4458</v>
+        <v>-0.3457</v>
       </c>
       <c r="O15" t="n">
-        <v>0.4057</v>
+        <v>1.7705</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.6829</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.5934</v>
+        <v>-2.0487</v>
       </c>
       <c r="R15" t="n">
-        <v>0.9105</v>
+        <v>2.0487</v>
       </c>
       <c r="S15" t="n">
-        <v>1.9228</v>
+        <v>-0.7153</v>
       </c>
       <c r="T15" t="n">
-        <v>2.6195</v>
+        <v>-0.407</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.6966</v>
+        <v>-0.3083</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.3389</v>
+        <v>-0.2006</v>
       </c>
       <c r="W15" t="n">
-        <v>1.405</v>
+        <v>0.7025</v>
       </c>
       <c r="X15" t="n">
-        <v>-2.7439</v>
+        <v>-0.9031</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. ABALDE</t>
+          <t>I. ALMANSA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.4969</v>
+        <v>2.0803</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.4797</v>
+        <v>3.9582</v>
       </c>
       <c r="F16" t="n">
-        <v>1.9765</v>
+        <v>-1.8779</v>
       </c>
       <c r="G16" t="n">
-        <v>3.5275</v>
+        <v>3.1452</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1263</v>
+        <v>2.5534</v>
       </c>
       <c r="I16" t="n">
-        <v>3.4013</v>
+        <v>0.5919</v>
       </c>
       <c r="J16" t="n">
-        <v>2.1027</v>
+        <v>3.1854</v>
       </c>
       <c r="K16" t="n">
-        <v>0.4719</v>
+        <v>2.9992</v>
       </c>
       <c r="L16" t="n">
-        <v>1.6308</v>
+        <v>0.1862</v>
       </c>
       <c r="M16" t="n">
-        <v>1.4249</v>
+        <v>-0.0402</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.3457</v>
+        <v>-0.4458</v>
       </c>
       <c r="O16" t="n">
-        <v>1.7705</v>
+        <v>0.4057</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.0487</v>
+        <v>-1.5934</v>
       </c>
       <c r="R16" t="n">
-        <v>2.0487</v>
+        <v>0.9105</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.83</v>
+        <v>0.9568</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.2361</v>
+        <v>0.9612000000000001</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5939</v>
+        <v>-0.0044</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.2006</v>
+        <v>-1.3389</v>
       </c>
       <c r="W16" t="n">
-        <v>0.7025</v>
+        <v>1.405</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.9031</v>
+        <v>-2.7439</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9689</v>
+        <v>1.4184</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.7314</v>
+        <v>-1.8499</v>
       </c>
       <c r="F17" t="n">
-        <v>2.7004</v>
+        <v>3.2682</v>
       </c>
       <c r="G17" t="n">
         <v>-0.1128</v>
@@ -1780,13 +1780,13 @@
         <v>1.8211</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.8478</v>
+        <v>-0.3984</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0643</v>
+        <v>-0.0541</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.9121</v>
+        <v>-0.3442</v>
       </c>
       <c r="V17" t="n">
         <v>1.9295</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4706</v>
+        <v>0.3917</v>
       </c>
       <c r="E18" t="n">
-        <v>1.7161</v>
+        <v>1.4792</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.2455</v>
+        <v>-1.0875</v>
       </c>
       <c r="G18" t="n">
         <v>-1.5275</v>
@@ -1858,13 +1858,13 @@
         <v>1.1382</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4226</v>
+        <v>0.3436</v>
       </c>
       <c r="T18" t="n">
-        <v>0.232</v>
+        <v>-0.0049</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1906</v>
+        <v>0.3485</v>
       </c>
       <c r="V18" t="n">
         <v>0.665</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>O. YURTSEVEN</t>
+          <t>A. FELIZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.5638</v>
+        <v>-0.2385</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.1248</v>
+        <v>-1.4113</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5609</v>
+        <v>1.1728</v>
       </c>
       <c r="G19" t="n">
-        <v>2.6411</v>
+        <v>0.9993</v>
       </c>
       <c r="H19" t="n">
-        <v>2.0479</v>
+        <v>1.106</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5931999999999999</v>
+        <v>-0.1067</v>
       </c>
       <c r="J19" t="n">
-        <v>3.0564</v>
+        <v>2.1289</v>
       </c>
       <c r="K19" t="n">
-        <v>2.982</v>
+        <v>2.0544</v>
       </c>
       <c r="L19" t="n">
         <v>0.0745</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.4154</v>
+        <v>-1.1296</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.9340000000000001</v>
+        <v>-0.9485</v>
       </c>
       <c r="O19" t="n">
-        <v>0.5187</v>
+        <v>-0.1811</v>
       </c>
       <c r="P19" t="n">
-        <v>-3.4145</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q19" t="n">
-        <v>-4.5526</v>
+        <v>-3.8697</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1382</v>
+        <v>1.8211</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5644</v>
+        <v>-0.1696</v>
       </c>
       <c r="T19" t="n">
-        <v>0.3714</v>
+        <v>-0.7599</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.9358</v>
+        <v>0.5903</v>
       </c>
       <c r="V19" t="n">
-        <v>0.7739</v>
+        <v>0.9805</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X19" t="n">
-        <v>0.7739</v>
+        <v>-0.1089</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. FELIZ</t>
+          <t>O. YURTSEVEN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.8772</v>
+        <v>-0.6347</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.7666</v>
+        <v>-1.4801</v>
       </c>
       <c r="F20" t="n">
-        <v>0.8894</v>
+        <v>0.8454</v>
       </c>
       <c r="G20" t="n">
-        <v>0.9993</v>
+        <v>2.6411</v>
       </c>
       <c r="H20" t="n">
-        <v>1.106</v>
+        <v>2.0479</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1067</v>
+        <v>0.5931999999999999</v>
       </c>
       <c r="J20" t="n">
-        <v>2.1289</v>
+        <v>3.0564</v>
       </c>
       <c r="K20" t="n">
-        <v>2.0544</v>
+        <v>2.982</v>
       </c>
       <c r="L20" t="n">
         <v>0.0745</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.1296</v>
+        <v>-0.4154</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.9485</v>
+        <v>-0.9340000000000001</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.1811</v>
+        <v>0.5187</v>
       </c>
       <c r="P20" t="n">
-        <v>-2.0487</v>
+        <v>-3.4145</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.8697</v>
+        <v>-4.5526</v>
       </c>
       <c r="R20" t="n">
-        <v>1.8211</v>
+        <v>1.1382</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8084</v>
+        <v>-0.6352</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.1152</v>
+        <v>0.0161</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3069</v>
+        <v>-0.6513</v>
       </c>
       <c r="V20" t="n">
-        <v>0.9805</v>
+        <v>0.7739</v>
       </c>
       <c r="W20" t="n">
-        <v>1.0895</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.1089</v>
+        <v>0.7739</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.3757</v>
+        <v>-0.7628</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.6286</v>
+        <v>-2.7995</v>
       </c>
       <c r="F21" t="n">
-        <v>2.253</v>
+        <v>2.0367</v>
       </c>
       <c r="G21" t="n">
         <v>1.5363</v>
@@ -2092,13 +2092,13 @@
         <v>1.5934</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.9796</v>
+        <v>-0.3668</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.0967</v>
+        <v>-0.2676</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1171</v>
+        <v>-0.0992</v>
       </c>
       <c r="V21" t="n">
         <v>-0.7942</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.916</v>
+        <v>-2.2994</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.7933</v>
+        <v>-4.5564</v>
       </c>
       <c r="F22" t="n">
-        <v>1.8773</v>
+        <v>2.2569</v>
       </c>
       <c r="G22" t="n">
         <v>-1.123</v>
@@ -2170,13 +2170,13 @@
         <v>1.8211</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.2053</v>
+        <v>-0.5887</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5162</v>
+        <v>-0.2793</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.6891</v>
+        <v>-0.3094</v>
       </c>
       <c r="V22" t="n">
         <v>-1.7259</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.6749</v>
+        <v>-3.5343</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.0391</v>
+        <v>-2.276</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.6358</v>
+        <v>-1.2583</v>
       </c>
       <c r="G23" t="n">
         <v>-2.9643</v>
@@ -2248,13 +2248,13 @@
         <v>1.3658</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4439</v>
+        <v>-0.3033</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1165</v>
+        <v>-0.3534</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3274</v>
+        <v>0.0501</v>
       </c>
       <c r="V23" t="n">
         <v>-0.2667</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.8011</v>
+        <v>-4.0997</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.2127</v>
+        <v>-3.8574</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.5884</v>
+        <v>-0.2423</v>
       </c>
       <c r="G24" t="n">
         <v>-4.3181</v>
@@ -2326,13 +2326,13 @@
         <v>1.1382</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.0083</v>
+        <v>-0.3068</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.3244</v>
+        <v>-0.969</v>
       </c>
       <c r="U24" t="n">
-        <v>0.3161</v>
+        <v>0.6622</v>
       </c>
       <c r="V24" t="n">
         <v>0.9805</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-8.225999999999999</v>
+        <v>-5.067399999999999</v>
       </c>
       <c r="E25" t="n">
         <v>-12.4437</v>
       </c>
       <c r="F25" t="n">
-        <v>4.217600000000001</v>
+        <v>7.376099999999999</v>
       </c>
       <c r="G25" t="n">
         <v>1.803699999999998</v>
@@ -2404,13 +2404,13 @@
         <v>14.7963</v>
       </c>
       <c r="S25" t="n">
-        <v>-5.3423</v>
+        <v>-2.1837</v>
       </c>
       <c r="T25" t="n">
         <v>-2.1179</v>
       </c>
       <c r="U25" t="n">
-        <v>-3.2242</v>
+        <v>-0.06569999999999998</v>
       </c>
       <c r="V25" t="n">
         <v>1.0031</v>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104758_W34.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104758_W34.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104758_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104758_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104758_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104758_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104758_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104758_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104758_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104758_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104758_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104758_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104758_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104758_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-7.167800000000002</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-0.9031</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104758_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-2.7439</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104758_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-0.2494</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104758_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-0.4245</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104758_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-0.1089</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104758_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0.7739</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104758_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-0.7942</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104758_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-1.3389</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104758_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-0.2667</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104758_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-0.1089</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104758_W34.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,7 @@
       <c r="X25" t="n">
         <v>-6.1646</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
